--- a/revision_v3/human_eval/Gold_Dev_Code_Review.xlsx
+++ b/revision_v3/human_eval/Gold_Dev_Code_Review.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,13 @@
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +81,16 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -89,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -125,6 +140,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -673,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -701,6 +722,15 @@
     <col width="45" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="45" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="80" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="80" customWidth="1" min="30" max="30"/>
+    <col width="80" customWidth="1" min="31" max="31"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="50" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -827,6 +857,51 @@
       <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>final_rationale</t>
+        </is>
+      </c>
+      <c r="Z1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_proposed_label</t>
+        </is>
+      </c>
+      <c r="AA1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_confidence</t>
+        </is>
+      </c>
+      <c r="AB1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_rationale</t>
+        </is>
+      </c>
+      <c r="AC1" s="11" t="inlineStr">
+        <is>
+          <t>source_static_analyzer_verdict</t>
+        </is>
+      </c>
+      <c r="AD1" s="11" t="inlineStr">
+        <is>
+          <t>source_static_analyzer_explanation</t>
+        </is>
+      </c>
+      <c r="AE1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_relevant_code_summary</t>
+        </is>
+      </c>
+      <c r="AF1" s="11" t="inlineStr">
+        <is>
+          <t>guard_tracer_result</t>
+        </is>
+      </c>
+      <c r="AG1" s="11" t="inlineStr">
+        <is>
+          <t>project_and_onchain_evidence</t>
+        </is>
+      </c>
+      <c r="AH1" s="11" t="inlineStr">
+        <is>
+          <t>opus5_unresolved_questions</t>
         </is>
       </c>
     </row>
@@ -956,6 +1031,63 @@
       <c r="W2" s="6" t="inlineStr"/>
       <c r="X2" s="8" t="inlineStr"/>
       <c r="Y2" s="8" t="inlineStr"/>
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: flush(): CALL at pc=767 to stored(sload) with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD2" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE2" s="12" t="inlineStr">
+        <is>
+          <t>1565-byte runtime on bnb exposing 5 dispatched function(s): initialized(), flush(), setReceiver(address), 0xda8120d8, receiver()
+Concern(s) found: flush(): CALL at pc=767 to stored(sload) with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; 0xda8120d8: SSTORE to slot 0x0 at pc=640 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Protection(s) found: msg.sender compared against a stored authority on setReceiver(address)
+Instruction census (whole contract): CALL×1, CALLER×2, SSTORE×2</t>
+        </is>
+      </c>
+      <c r="AF2" s="12" t="inlineStr">
+        <is>
+          <t>• initialized(): no sensitive operation reachable
+• flush(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• setReceiver(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• 0xda8120d8: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• receiver(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG2" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1565 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 5, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 20, "type": "bool", "n_reads": 2, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH2" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -1083,6 +1215,58 @@
       <c r="W3" s="9" t="inlineStr"/>
       <c r="X3" s="8" t="inlineStr"/>
       <c r="Y3" s="8" t="inlineStr"/>
+      <c r="Z3" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xa3cbe5af: msg.sender must equal the hardcoded address 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD3" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE3" s="12" t="inlineStr">
+        <is>
+          <t>2741-byte runtime on arbitrum exposing 1 dispatched function(s): 0xa3cbe5af
+Concern(s) found: 0xa3cbe5af: msg.sender must equal the hardcoded address 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa3cbe5af: msg.sender must equal the hardcoded address 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa3cbe5af: msg.sender must equal the hardcoded address 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa3cbe5af: msg.sender must equal the hardcoded address 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa3cbe5af: msg.sender must equal the hardcoded address 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa3cbe5af: msg.sender must equal the hardcoded address 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×3, CALLER×6</t>
+        </is>
+      </c>
+      <c r="AF3" s="12" t="inlineStr">
+        <is>
+          <t>• 0xa3cbe5af: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3; hardcoded_address_check against 0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3</t>
+        </is>
+      </c>
+      <c r="AG3" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=2741 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+addresses embedded in the code: [{"bytecode_offset": 40, "address": "0x31a00175e7be8d8ba5453cfbf6c9be721069b32e"}, {"bytecode_offset": 261, "address": "0xda6b5f1fd0b81ed81ddb9ad84f07912b3ee21de3"}, {"bytecode_offset": 334, "address": "0x1f77528c1a66ba2dcbdeaf6cf471323333e91c9b"}, {"bytecode_offset": 408, "address": "0x33f07d2b00ca</t>
+        </is>
+      </c>
+      <c r="AH3" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1210,6 +1394,61 @@
       <c r="W4" s="6" t="inlineStr"/>
       <c r="X4" s="8" t="inlineStr"/>
       <c r="Y4" s="8" t="inlineStr"/>
+      <c r="Z4" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA4" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB4" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: Transfer(address): CALL at pc=722 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD4" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE4" s="12" t="inlineStr">
+        <is>
+          <t>3560-byte runtime on arbitrum exposing 3 dispatched function(s): Transfer(address), 0x688cbba1, 0xbc6e461a Embedded strings mention: Multicall.
+Concern(s) found: Transfer(address): CALL at pc=722 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x688cbba1: CALL at pc=722 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xbc6e461a: CALL at pc=1559 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): ADDRESS×1, CALL×4, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF4" s="12" t="inlineStr">
+        <is>
+          <t>• Transfer(address): an unauthenticated path to a sensitive operation exists
+• 0x688cbba1: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• 0xbc6e461a: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG4" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=3560 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+addresses embedded in the code: [{"bytecode_offset": 240, "address": "0xb34fd47bdc979c311830f8162aeda26f4796c758"}]</t>
+        </is>
+      </c>
+      <c r="AH4" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1102]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x688cbba1, 0xbc6e461a; unauthenticated call(s) forwarding only msg.value to a fixed destination ([('0xbc6e461a', 374, '0xb34fd47bdc979c311830f8162aeda26f4796c758')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1337,6 +1576,65 @@
       <c r="W5" s="9" t="inlineStr"/>
       <c r="X5" s="8" t="inlineStr"/>
       <c r="Y5" s="8" t="inlineStr"/>
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: rescueETH(): msg.sender must equal the hardcoded address 0xdc8f3744804d44a367d94ff6accbe8cd4c5a8535. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD5" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE5" s="12" t="inlineStr">
+        <is>
+          <t>3940-byte runtime on ethereum exposing 7 dispatched function(s): 0x02c6e7da, rescueETH(), rescueTokens(address,uint256), recipient(), owner(), undelegate(), 0xd889d02b Embedded strings mention: Not owner, Unauthorized.
+Concern(s) found: rescueETH(): msg.sender must equal the hardcoded address 0xdc8f3744804d44a367d94ff6accbe8cd4c5a8535. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; rescueTokens(address,uint256): msg.sender must equal the hardcoded address 0xdc8f3744804d44a367d94ff6accbe8cd4c5a8535. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×5, CALLER×4</t>
+        </is>
+      </c>
+      <c r="AF5" s="12" t="inlineStr">
+        <is>
+          <t>• 0x02c6e7da: no sensitive operation reachable
+• rescueETH(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xdc8f3744804d44a367d94ff6accbe8cd4c5a8535
+• rescueTokens(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xdc8f3744804d44a367d94ff6accbe8cd4c5a8535 [analysis incomplete for this function]
+• recipient(): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• undelegate(): no sensitive operation reachable
+• 0xd889d02b: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG5" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3940 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 439, "address": "0x4050bdbef63a00415e67b2f691bd8ff52e4215bb"}]</t>
+        </is>
+      </c>
+      <c r="AH5" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [857, 2071]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: rescueTokens(address,uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1464,6 +1762,69 @@
       <c r="W6" s="6" t="inlineStr"/>
       <c r="X6" s="8" t="inlineStr"/>
       <c r="Y6" s="8" t="inlineStr"/>
+      <c r="Z6" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA6" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: sweepERC20(address): CALL at pc=3446 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD6" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE6" s="12" t="inlineStr">
+        <is>
+          <t>8784-byte runtime on base exposing 10 dispatched function(s): supportsInterface(bytes4), onERC721Received(address,address,uint256,bytes), execute(address,bytes), 0x3b175d70, 0x6054c38e, multicall(address[],bytes[]), onERC1155BatchReceived(address,address,uint256[],uint256[],bytes), sweepERC20(address), onERC1155Received(address,address,uint256,uint256,bytes), 0xfd559ebc
+Concern(s) found: sweepERC20(address): CALL at pc=3446 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Protection(s) found: msg.sender compared against a stored authority on 0x6054c38e, execute(address,bytes), multicall(address[],bytes[])
+Instruction census (whole contract): ADDRESS×5, CALL×9, CALLER×8, SSTORE×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF6" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• execute(address,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• 0x3b175d70: no sensitive operation reachable
+• 0x6054c38e: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check
+• multicall(address[],bytes[]): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• sweepERC20(address): an unauthenticated path to a sensitive operation exists
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• 0xfd559ebc: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 5 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG6" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=8784 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 9, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH6" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1244, 2791, 3105, 3692]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1591,6 +1952,61 @@
       <c r="W7" s="9" t="inlineStr"/>
       <c r="X7" s="8" t="inlineStr"/>
       <c r="Y7" s="8" t="inlineStr"/>
+      <c r="Z7" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA7" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB7" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: aggregate3Value((address,bool,uint256,bytes)[]): CALL at pc=611 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC7" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD7" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE7" s="12" t="inlineStr">
+        <is>
+          <t>3161-byte runtime on base exposing 5 dispatched function(s): aggregate3Value((address,bool,uint256,bytes)[]), aggregate((address,bytes)[]), aggregate3((address,bool,bytes)[]), withdrawToken(address), withdrawETH() Embedded strings mention: Multicall.
+Concern(s) found: aggregate3Value((address,bool,uint256,bytes)[]): CALL at pc=611 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; aggregate((address,bytes)[]): CALL at pc=1113 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; aggregate3((address,bool,bytes)[]): CALL at pc=1576 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; withdrawToken(address): CALL at pc=2014 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; withdrawETH(): CALL at pc=303 to 0x000029a2a5245b1e3f5fabee3c7c75a7c9875efd with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×1, CALL×5, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF7" s="12" t="inlineStr">
+        <is>
+          <t>• aggregate3Value((address,bool,uint256,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• aggregate((address,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• aggregate3((address,bool,bytes)[]): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• withdrawToken(address): an unauthenticated path to a sensitive operation exists
+• withdrawETH(): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG7" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=3161 bytes
+verified source=False
+other chains with identical bytecode: ["base", "ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH7" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: aggregate((address,bytes)[]), aggregate3((address,bool,bytes)[]), aggregate3Value((address,bool,uint256,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1718,6 +2134,59 @@
       <c r="W8" s="6" t="inlineStr"/>
       <c r="X8" s="8" t="inlineStr"/>
       <c r="Y8" s="8" t="inlineStr"/>
+      <c r="Z8" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA8" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB8" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [785]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC8" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD8" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE8" s="12" t="inlineStr">
+        <is>
+          <t>810-byte runtime on bnb exposing 2 dispatched function(s): 0xda8120d8, receiver()
+Instruction census (whole contract): CALL×1, CALLCODE×1, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF8" s="12" t="inlineStr">
+        <is>
+          <t>• 0xda8120d8: no sensitive operation reachable
+• receiver(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG8" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=810 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH8" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALLCODE': [785]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
@@ -1845,6 +2314,66 @@
       <c r="W9" s="9" t="inlineStr"/>
       <c r="X9" s="8" t="inlineStr"/>
       <c r="Y9" s="8" t="inlineStr"/>
+      <c r="Z9" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA9" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB9" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: burn(): CALL at pc=3675 to 0x17d37a63d9f2a9e49aabfc5de68060b1036d91dc with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC9" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD9" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE9" s="12" t="inlineStr">
+        <is>
+          <t>7282-byte runtime on ethereum exposing 8 dispatched function(s): 0x13236d04, 0x1d073a7a, ROUTER(), weth(), burn(), WETH(), UNISWAP_V3_FACTORY(), router()
+Concern(s) found: burn(): CALL at pc=3675 to 0x17d37a63d9f2a9e49aabfc5de68060b1036d91dc with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; burn(): CALL at pc=3748 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×3, CALL×11, CALLER×1, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF9" s="12" t="inlineStr">
+        <is>
+          <t>• 0x13236d04: no sensitive operation reachable
+• 0x1d073a7a: no sensitive operation reachable
+• ROUTER(): no sensitive operation reachable
+• weth(): no sensitive operation reachable
+• burn(): an unauthenticated path to a sensitive operation exists
+• WETH(): no sensitive operation reachable
+• UNISWAP_V3_FACTORY(): no sensitive operation reachable
+• router(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 7 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG9" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=7282 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 132, "address": "0x17d37a63d9f2a9e49aabfc5de68060b1036d91dc"}, {"bytecode_offset": 1972, "address": "0x1f98431c8ad98523631ae4a59f267346ea31f984"}, {"bytecode_offset": 2021, "address": "0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2"}, {"bytecode_offset": 2363, "address": "0xe592427a</t>
+        </is>
+      </c>
+      <c r="AH9" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1081, 1319, 1557, 2426]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1972,6 +2501,60 @@
       <c r="W10" s="6" t="inlineStr"/>
       <c r="X10" s="8" t="inlineStr"/>
       <c r="Y10" s="8" t="inlineStr"/>
+      <c r="Z10" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA10" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB10" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: initialize(address): SSTORE to slot 0x0 at pc=487 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC10" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD10" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE10" s="12" t="inlineStr">
+        <is>
+          <t>722-byte runtime on ethereum exposing 2 dispatched function(s): destination(), initialize(address)
+Concern(s) found: initialize(address): SSTORE to slot 0x0 at pc=487 with no authorization branch — in the EOA's own (initially empty) storage this lets the first caller install whatever authority that slot controls
+Instruction census (whole contract): CALL×1, CALLER×2, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF10" s="12" t="inlineStr">
+        <is>
+          <t>• destination(): no sensitive operation reachable
+• initialize(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG10" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=722 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 2, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 406, "address": "0x60256154ce536b5379826d72cf5110ec29d190ff"}]</t>
+        </is>
+      </c>
+      <c r="AH10" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -2099,6 +2682,64 @@
       <c r="W11" s="9" t="inlineStr"/>
       <c r="X11" s="8" t="inlineStr"/>
       <c r="Y11" s="8" t="inlineStr"/>
+      <c r="Z11" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA11" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB11" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transferFrom(address,address): CALL at pc=1057 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC11" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD11" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE11" s="12" t="inlineStr">
+        <is>
+          <t>3401-byte runtime on ethereum exposing 7 dispatched function(s): transferFrom(address,address), transferFrom(address,address,address,uint256), transfer(address), refunds(), execute(address,uint256,bytes), transfer(address,address,uint256), transferEth(address,uint256)
+Concern(s) found: transferFrom(address,address): CALL at pc=1057 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; transfer(address): CALL at pc=1574 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; refunds(): CALL at pc=1731 to 0x00b700b9da0053009cb84400ed1e8fe251002af3 with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; transferFrom(address,address,address,uint256): tx.origin must equal the hardcoded address 0x00b700b9da0053009cb84400ed1e8fe251002af3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; execute(address,uint256,bytes): tx.origin must equal the hardcoded address 0x00b700b9da0053009cb84400ed1e8fe251002af3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; transfer(address,address,uint256): tx.origin must equal the hardcoded address 0x00b700b9da0053009cb84400ed1e8fe251002af3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; transferEth(address,uint256): tx.origin must equal the hardcoded address 0x00b700b9da0053009cb84400ed1e8fe251002af3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×3, CALL×8, CALLER×1, ORIGIN×1, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF11" s="12" t="inlineStr">
+        <is>
+          <t>• transferFrom(address,address): an unauthenticated path to a sensitive operation exists
+• transferFrom(address,address,address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x00b700b9da0053009cb84400ed1e8fe251002af3
+• transfer(address): an unauthenticated path to a sensitive operation exists
+• refunds(): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• execute(address,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x00b700b9da0053009cb84400ed1e8fe251002af3 [analysis incomplete for this function]
+• transfer(address,address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x00b700b9da0053009cb84400ed1e8fe251002af3
+• transferEth(address,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x00b700b9da0053009cb84400ed1e8fe251002af3 [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG11" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=3401 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 1843, "address": "0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2"}]</t>
+        </is>
+      </c>
+      <c r="AH11" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: execute(address,uint256,bytes), refunds(), transferEth(address,uint256); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: refunds() pc=1574 -&gt; 0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2226,6 +2867,63 @@
       <c r="W12" s="6" t="inlineStr"/>
       <c r="X12" s="8" t="inlineStr"/>
       <c r="Y12" s="8" t="inlineStr"/>
+      <c r="Z12" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA12" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB12" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0725602e: CALL at pc=1736 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC12" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD12" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE12" s="12" t="inlineStr">
+        <is>
+          <t>2491-byte runtime on base exposing 6 dispatched function(s): 0x0725602e, disable(), isDisabled(), 0x80c3da8d, sweepETH(), sweepTokens(address)
+Concern(s) found: 0x0725602e: CALL at pc=1736 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x80c3da8d: CALL at pc=908 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; sweepTokens(address): CALL at pc=1488 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; sweepETH(): CALL at pc=381 to 0x90d8a3915124d1b7d3343670a06c4d3c0ceff4f1 with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; disable(): msg.sender must equal the hardcoded address 0x0835001cec7823dfc41270ff0c6551c3f9422222. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×4, CALLER×3, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF12" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0725602e: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• disable(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x0835001cec7823dfc41270ff0c6551c3f9422222
+• isDisabled(): no sensitive operation reachable
+• 0x80c3da8d: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• sweepETH(): an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• sweepTokens(address): an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG12" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2491 bytes
+verified source=True
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "bool", "n_reads": 5, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH12" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) forwarding only msg.value to a fixed destination ([('0x0725602e', 381, '0x90d8a3915124d1b7d3343670a06c4d3c0ceff4f1'), ('0x80c3da8d', 381, '0x90d8a3915124d1b7d3343670a06c4d3c0ceff4f1')]) — a caller can only donate their own ETH, so this is not by itself a path to the account's assets</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -2353,6 +3051,60 @@
       <c r="W13" s="9" t="inlineStr"/>
       <c r="X13" s="8" t="inlineStr"/>
       <c r="Y13" s="8" t="inlineStr"/>
+      <c r="Z13" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA13" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB13" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: withdrawAnyToken(address): msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC13" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD13" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE13" s="12" t="inlineStr">
+        <is>
+          <t>871-byte runtime on bnb exposing 2 dispatched function(s): withdrawAnyToken(address), 0xa9f5cd83
+Concern(s) found: withdrawAnyToken(address): msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xa9f5cd83: msg.sender must equal the hardcoded address 0x3e577385fe768238d525b04cb25fae7c0e700000. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×2, CALLER×5, SSTORE×3, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF13" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawAnyToken(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3e577385fe768238d525b04cb25fae7c0e700000
+• 0xa9f5cd83: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x3e577385fe768238d525b04cb25fae7c0e700000</t>
+        </is>
+      </c>
+      <c r="AG13" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=871 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(address =&gt; uint8)", "n_reads": 0, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 77, "address": "0x3e577385fe768238d525b04cb25fae7c0e700000"}]</t>
+        </is>
+      </c>
+      <c r="AH13" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2480,6 +3232,59 @@
       <c r="W14" s="6" t="inlineStr"/>
       <c r="X14" s="8" t="inlineStr"/>
       <c r="Y14" s="8" t="inlineStr"/>
+      <c r="Z14" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA14" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB14" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [815], 'CREATE2': [1791]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC14" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD14" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE14" s="12" t="inlineStr">
+        <is>
+          <t>1808-byte runtime on base exposing 2 dispatched function(s): recipient(), sweep(address[])
+Instruction census (whole contract): ADDRESS×1, CALL×2, CALLER×1, CREATE2×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF14" s="12" t="inlineStr">
+        <is>
+          <t>• recipient(): no sensitive operation reachable
+• sweep(address[]): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG14" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1808 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+addresses embedded in the code: [{"bytecode_offset": 171, "address": "0xb6db24cf73c54def808d4ceb04d444a1d5e93aae"}]</t>
+        </is>
+      </c>
+      <c r="AH14" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [815], 'CREATE2': [1791]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -2607,6 +3412,63 @@
       <c r="W15" s="9" t="inlineStr"/>
       <c r="X15" s="8" t="inlineStr"/>
       <c r="Y15" s="8" t="inlineStr"/>
+      <c r="Z15" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA15" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB15" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: msg.sender compared against a stored authority on changeAdmin(address), upgradeTo(address), upgradeToAndCall(address,bytes) The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC15" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD15" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The reachability the rule asserts is reproduced (an external call is reachable from receive()/fallback()), but every such path passes an authorization branch. The rule is correct about capability and silent about authorization, which is its documented limitation — it has no guard predicate. This is capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
+      <c r="AE15" s="12" t="inlineStr">
+        <is>
+          <t>1852-byte runtime on base exposing 5 dispatched function(s): upgradeTo(address), upgradeToAndCall(address,bytes), implementation(), changeAdmin(address), admin()
+Protection(s) found: msg.sender compared against a stored authority on changeAdmin(address), upgradeTo(address), upgradeToAndCall(address,bytes)
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×4, DELEGATECALL×1, SSTORE×2</t>
+        </is>
+      </c>
+      <c r="AF15" s="12" t="inlineStr">
+        <is>
+          <t>• upgradeTo(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• upgradeToAndCall(address,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• implementation(): no sensitive operation reachable
+• changeAdmin(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• admin(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG15" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1852 bytes
+verified source=True
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "10d6a54a4754c8869d6886b5f5d7fbfa5b4522237ea5c60d11bc4e7a1ff9390b", "offset": 0, "type": "address", "n_reads": 4, "n_writes": 1}, {"slot": "7050c9e0f4ca769c69bd3a8ef740bc37934f8e2c036e5a723fd8ee048ed3f8c3", "offset": 0, "type": "address", "n_reads": 4, "n_writes": 2}]
+addresses embedded in the code: [{"bytecode_offset": 1747, "address": "0x657420612070726f787920696d706c656d656e74"}]</t>
+        </is>
+      </c>
+      <c r="AH15" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -2734,6 +3596,58 @@
       <c r="W16" s="6" t="inlineStr"/>
       <c r="X16" s="8" t="inlineStr"/>
       <c r="Y16" s="8" t="inlineStr"/>
+      <c r="Z16" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA16" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB16" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x1934bea6: CALL at pc=312 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC16" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD16" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE16" s="12" t="inlineStr">
+        <is>
+          <t>1329-byte runtime on bnb exposing 1 dispatched function(s): 0x1934bea6
+Concern(s) found: 0x1934bea6: CALL at pc=312 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x1934bea6: CALL at pc=440 to 0xa5ba6c33bb954a7e42244631a3fc6a30b011b1a3 with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): CALL×3, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF16" s="12" t="inlineStr">
+        <is>
+          <t>• 0x1934bea6: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG16" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1329 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 39, "address": "0xa5ba6c33bb954a7e42244631a3fc6a30b011b1a3"}]</t>
+        </is>
+      </c>
+      <c r="AH16" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
@@ -2861,6 +3775,57 @@
       <c r="W17" s="9" t="inlineStr"/>
       <c r="X17" s="8" t="inlineStr"/>
       <c r="Y17" s="8" t="inlineStr"/>
+      <c r="Z17" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA17" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB17" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: test(address): CALL at pc=91 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC17" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD17" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE17" s="12" t="inlineStr">
+        <is>
+          <t>252-byte runtime on base exposing 1 dispatched function(s): test(address)
+Concern(s) found: test(address): CALL at pc=91 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): CALL×2, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF17" s="12" t="inlineStr">
+        <is>
+          <t>• test(address): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG17" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=252 bytes
+verified source=False
+other chains with identical bytecode: ["base", "bnb", "ethereum", "optimism"]</t>
+        </is>
+      </c>
+      <c r="AH17" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2988,6 +3953,57 @@
       <c r="W18" s="6" t="inlineStr"/>
       <c r="X18" s="8" t="inlineStr"/>
       <c r="Y18" s="8" t="inlineStr"/>
+      <c r="Z18" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA18" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB18" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x040113fc: tx.origin must equal the hardcoded address 0x9dcb4cd97a2e871834659fee2c837d2432c54caa. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC18" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD18" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): fallback()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE18" s="12" t="inlineStr">
+        <is>
+          <t>1937-byte runtime on base exposing 1 dispatched function(s): 0x040113fc Embedded strings mention: Not owner.
+Concern(s) found: 0x040113fc: tx.origin must equal the hardcoded address 0x9dcb4cd97a2e871834659fee2c837d2432c54caa. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, CALLER×1, ORIGIN×1</t>
+        </is>
+      </c>
+      <c r="AF18" s="12" t="inlineStr">
+        <is>
+          <t>• 0x040113fc: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x9dcb4cd97a2e871834659fee2c837d2432c54caa</t>
+        </is>
+      </c>
+      <c r="AG18" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=1937 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH18" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
@@ -3115,6 +4131,59 @@
       <c r="W19" s="9" t="inlineStr"/>
       <c r="X19" s="8" t="inlineStr"/>
       <c r="Y19" s="8" t="inlineStr"/>
+      <c r="Z19" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA19" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB19" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1, 'CREATE2': 1, 'SELFDESTRUCT': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1, CREATE2x1, SELFDESTRUCTx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC19" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD19" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule fired on 1 tuple(s) (enclosing function(s): receive()). An independent CFG re-derivation confirms an external call is reachable from the receive()/fallback() path, and confirms it is reachable without passing any caller-authorization branch. The rule's reachability claim holds and, here, the stronger unauthenticated-access claim holds too.</t>
+        </is>
+      </c>
+      <c r="AE19" s="12" t="inlineStr">
+        <is>
+          <t>331-byte runtime on base exposing 1 dispatched function(s): RECIPIENT()
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1, 'CREATE2': 1, 'SELFDESTRUCT': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1, CREATE2x1, SELFDESTRUCTx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1, CREATE2×1, SELFDESTRUCT×1</t>
+        </is>
+      </c>
+      <c r="AF19" s="12" t="inlineStr">
+        <is>
+          <t>• RECIPIENT(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG19" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=331 bytes
+verified source=False
+other chains with identical bytecode: ["base", "optimism"]
+addresses embedded in the code: [{"bytecode_offset": 32, "address": "0x6a97eada929869c9419b23eeedefb4ca763badf2"}]</t>
+        </is>
+      </c>
+      <c r="AH19" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [290], 'SELFDESTRUCT': [310]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -3242,6 +4311,58 @@
       <c r="W20" s="6" t="inlineStr"/>
       <c r="X20" s="8" t="inlineStr"/>
       <c r="Y20" s="8" t="inlineStr"/>
+      <c r="Z20" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB20" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [800]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC20" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD20" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule reports an external call reachable from receive()/fallback(), but an independent CFG re-derivation with a non-matching selector could not reach any external call on that path. Possible causes: Gigahorse and this analyzer recover different control flow, the call sits behind a path this traversal did not explore, or the rule attributed a call from a normal selector to the fallback. Treated as evidence in tension, not as a refutation.</t>
+        </is>
+      </c>
+      <c r="AE20" s="12" t="inlineStr">
+        <is>
+          <t>2737-byte runtime on base exposing 1 dispatched function(s): OWNER() Embedded strings mention: Router.
+Instruction census (whole contract): CALL×1, CALLER×2, ORIGIN×2</t>
+        </is>
+      </c>
+      <c r="AF20" s="12" t="inlineStr">
+        <is>
+          <t>• OWNER(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG20" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2737 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+addresses embedded in the code: [{"bytecode_offset": 103, "address": "0x9dcb4cd97a2e871834659fee2c837d2432c54caa"}]</t>
+        </is>
+      </c>
+      <c r="AH20" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [800]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
@@ -3369,6 +4490,59 @@
       <c r="W21" s="9" t="inlineStr"/>
       <c r="X21" s="8" t="inlineStr"/>
       <c r="Y21" s="8" t="inlineStr"/>
+      <c r="Z21" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA21" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB21" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: transfer(address,uint256): CALL at pc=340 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC21" s="12" t="inlineStr">
+        <is>
+          <t>positive — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD21" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer FLAGGED this contract. Its rule is a single reachability test: 'an external call is reachable from receive() or fallback()'. It contains no authorization check at all, so a flag means a powerful operation can be reached from an entry point that carries no caller check at dispatch time — it does NOT by itself mean access control is missing.
+Assessment against the control-flow evidence for this item: The rule reports an external call reachable from receive()/fallback(), but an independent CFG re-derivation with a non-matching selector could not reach any external call on that path. Possible causes: Gigahorse and this analyzer recover different control flow, the call sits behind a path this traversal did not explore, or the rule attributed a call from a normal selector to the fallback. Treated as evidence in tension, not as a refutation.</t>
+        </is>
+      </c>
+      <c r="AE21" s="12" t="inlineStr">
+        <is>
+          <t>1951-byte runtime on bnb exposing 2 dispatched function(s): transfer(address,uint256), 0xd77ddcc9
+Concern(s) found: transfer(address,uint256): CALL at pc=340 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; transfer(address,uint256): CALL at pc=478 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xd77ddcc9: CALL at pc=744 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): CALL×3, CALLER×1, CREATE×1</t>
+        </is>
+      </c>
+      <c r="AF21" s="12" t="inlineStr">
+        <is>
+          <t>• transfer(address,uint256): an unauthenticated path to a sensitive operation exists
+• 0xd77ddcc9: an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG21" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1951 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH21" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CREATE': [1910]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -3496,6 +4670,58 @@
       <c r="W22" s="6" t="inlineStr"/>
       <c r="X22" s="8" t="inlineStr"/>
       <c r="Y22" s="8" t="inlineStr"/>
+      <c r="Z22" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA22" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB22" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC22" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD22" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE22" s="12" t="inlineStr">
+        <is>
+          <t>828-byte runtime on ethereum exposing 1 dispatched function(s): withdrawTokens(address,address,uint256)
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF22" s="12" t="inlineStr">
+        <is>
+          <t>• withdrawTokens(address,address,uint256): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG22" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=828 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH22" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [145]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
@@ -3603,6 +4829,59 @@
       <c r="W23" s="9" t="inlineStr"/>
       <c r="X23" s="8" t="inlineStr"/>
       <c r="Y23" s="8" t="inlineStr"/>
+      <c r="Z23" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA23" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB23" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: DELEGATECALL at pc=347 to ['memory'] reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC23" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD23" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE23" s="12" t="inlineStr">
+        <is>
+          <t>455-byte runtime on base exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: DELEGATECALL at pc=347 to ['memory'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; &lt;no dispatcher recovered; analysed from pc=0&gt;: DELEGATECALL at pc=430 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage
+Protection(s) found: msg.sender compared against a stored authority on &lt;no dispatcher recovered; analysed from pc=0&gt;
+Instruction census (whole contract): ADDRESS×1, CALLER×1, DELEGATECALL×2, SSTORE×2, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF23" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists — check found: storage_based_caller_check; storage_condition</t>
+        </is>
+      </c>
+      <c r="AG23" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=455 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 0}, {"slot": "360894a13ba1a3210667c828492db98dca3e2076cc3735a920a3ca505d382bbc", "offset": 0, "type": "uint256", "n_reads": 0, "n_writes": 0}, {"slot": "b53127684a5</t>
+        </is>
+      </c>
+      <c r="AH23" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3730,6 +5009,58 @@
       <c r="W24" s="6" t="inlineStr"/>
       <c r="X24" s="8" t="inlineStr"/>
       <c r="Y24" s="8" t="inlineStr"/>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA24" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB24" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xab7e4c70: CALL at pc=337 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC24" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD24" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE24" s="12" t="inlineStr">
+        <is>
+          <t>2190-byte runtime on base exposing 2 dispatched function(s): 0xab7e4c70, 0xca4952d4
+Concern(s) found: 0xab7e4c70: CALL at pc=337 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0xca4952d4: CALL at pc=784 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): CALL×2, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF24" s="12" t="inlineStr">
+        <is>
+          <t>• 0xab7e4c70: an unauthenticated path to a sensitive operation exists
+• 0xca4952d4: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG24" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2190 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH24" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -3857,6 +5188,57 @@
       <c r="W25" s="9" t="inlineStr"/>
       <c r="X25" s="8" t="inlineStr"/>
       <c r="Y25" s="8" t="inlineStr"/>
+      <c r="Z25" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA25" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB25" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: execute(address,uint256,bytes): CALL at pc=134 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC25" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD25" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE25" s="12" t="inlineStr">
+        <is>
+          <t>652-byte runtime on base exposing 1 dispatched function(s): execute(address,uint256,bytes)
+Concern(s) found: execute(address,uint256,bytes): CALL at pc=134 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF25" s="12" t="inlineStr">
+        <is>
+          <t>• execute(address,uint256,bytes): an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG25" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=652 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH25" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: execute(address,uint256,bytes)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3964,6 +5346,58 @@
       <c r="W26" s="6" t="inlineStr"/>
       <c r="X26" s="8" t="inlineStr"/>
       <c r="Y26" s="8" t="inlineStr"/>
+      <c r="Z26" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB26" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=75 to 0xbb7218d77f06a89c15e9188b1f1b427ae8f0290c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC26" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD26" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE26" s="12" t="inlineStr">
+        <is>
+          <t>243-byte runtime on base exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=75 to 0xbb7218d77f06a89c15e9188b1f1b427ae8f0290c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): CALL×1, CALLER×1</t>
+        </is>
+      </c>
+      <c r="AF26" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG26" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=243 bytes
+verified source=False
+other chains with identical bytecode: ["base", "bnb", "ethereum", "optimism"]
+addresses embedded in the code: [{"bytecode_offset": 10, "address": "0xbb7218d77f06a89c15e9188b1f1b427ae8f0290c"}]</t>
+        </is>
+      </c>
+      <c r="AH26" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
@@ -4091,6 +5525,59 @@
       <c r="W27" s="9" t="inlineStr"/>
       <c r="X27" s="8" t="inlineStr"/>
       <c r="Y27" s="8" t="inlineStr"/>
+      <c r="Z27" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA27" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB27" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x2bd5dea8: msg.sender must equal the hardcoded address 0x7ce2abaa9237b8d2517a169d833c9b61c0a70d6b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC27" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD27" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE27" s="12" t="inlineStr">
+        <is>
+          <t>1938-byte runtime on optimism exposing 2 dispatched function(s): 0x2bd5dea8, 0xe9524386
+Concern(s) found: 0x2bd5dea8: msg.sender must equal the hardcoded address 0x7ce2abaa9237b8d2517a169d833c9b61c0a70d6b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xe9524386: msg.sender must equal the hardcoded address 0x7ce2abaa9237b8d2517a169d833c9b61c0a70d6b. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF27" s="12" t="inlineStr">
+        <is>
+          <t>• 0x2bd5dea8: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x7ce2abaa9237b8d2517a169d833c9b61c0a70d6b [analysis incomplete for this function]
+• 0xe9524386: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x7ce2abaa9237b8d2517a169d833c9b61c0a70d6b [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG27" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=1938 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+addresses embedded in the code: [{"bytecode_offset": 163, "address": "0x7ce2abaa9237b8d2517a169d833c9b61c0a70d6b"}]</t>
+        </is>
+      </c>
+      <c r="AH27" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x2bd5dea8, 0xe9524386</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4218,6 +5705,56 @@
       <c r="W28" s="6" t="inlineStr"/>
       <c r="X28" s="8" t="inlineStr"/>
       <c r="Y28" s="8" t="inlineStr"/>
+      <c r="Z28" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA28" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB28" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC28" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD28" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer. An external call is reachable from the fallback/receive path but only behind an authorization branch, which is consistent with the rule staying silent (though the rule would have fired on reachability alone, so agreement here is coincidental rather than principled).</t>
+        </is>
+      </c>
+      <c r="AE28" s="12" t="inlineStr">
+        <is>
+          <t>2567-byte runtime on ethereum exposing 1 dispatched function(s): getCallers()
+Instruction census (whole contract): CALL×1, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF28" s="12" t="inlineStr">
+        <is>
+          <t>• getCallers(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG28" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2567 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH28" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
@@ -4345,6 +5882,59 @@
       <c r="W29" s="9" t="inlineStr"/>
       <c r="X29" s="8" t="inlineStr"/>
       <c r="Y29" s="8" t="inlineStr"/>
+      <c r="Z29" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA29" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB29" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [165, 499, 673, 1006]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC29" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD29" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE29" s="12" t="inlineStr">
+        <is>
+          <t>2082-byte runtime on ethereum exposing 2 dispatched function(s): 0x8cabfe01, 0xe02bf96d
+Instruction census (whole contract): ADDRESS×2, CALL×4, CALLER×1, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF29" s="12" t="inlineStr">
+        <is>
+          <t>• 0x8cabfe01: no sensitive operation reachable
+• 0xe02bf96d: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG29" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2082 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 436, "address": "0xea459dde8dd4e1b28324ff1a1dcffedfec596db0"}]</t>
+        </is>
+      </c>
+      <c r="AH29" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [165, 499, 673, 1006]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4472,6 +6062,76 @@
       <c r="W30" s="6" t="inlineStr"/>
       <c r="X30" s="8" t="inlineStr"/>
       <c r="Y30" s="8" t="inlineStr"/>
+      <c r="Z30" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA30" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB30" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: execute(bytes32,bytes): CALL at pc=3761 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC30" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD30" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE30" s="12" t="inlineStr">
+        <is>
+          <t>6792-byte runtime on polygon exposing 16 dispatched function(s): supportsInterface(bytes4), onERC721Received(address,address,uint256,bytes), isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256), getNonce(uint192), removeValidator(address), addValidator(address), 0x75f25167, eip712Domain(), executeUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32)
+Concern(s) found: execute(bytes32,bytes): CALL at pc=3761 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; execute(bytes32,bytes): CALL at pc=3921 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; execute(bytes32,bytes): CALL at pc=3207 to unresolved with value from calldata, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Protection(s) found: self-call restriction (msg.sender == address(this)) on addValidator(address), execute(bytes32,bytes), invalidateNonce(uint256), removeValidator(address) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on execute(bytes32,bytes), isValidSignature(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256); caller restricted to a recognized ERC-4337 EntryPoint on executeUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256)
+Instruction census (whole contract): ADDRESS×9, CALL×6, CALLER×10, CREATE2×2, ORIGIN×1, SSTORE×4, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF30" s="12" t="inlineStr">
+        <is>
+          <t>• supportsInterface(bytes4): no sensitive operation reachable
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• isValidSignature(bytes32,bytes): no sensitive operation reachable — check found: storage_condition; signature_authorization
+• validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x4337084d9e255ff0702461cf8895ce9e3b5ff108; storage_condition [analysis incomplete for this function]
+• getNonce(uint192): no sensitive operation reachable
+• removeValidator(address): every path to a sensitive operation passes an authorization check — check found: self_call_check
+• addValidator(address): every path to a sensitive operation passes an authorization check — check found: self_call_check
+• 0x75f25167: no sensitive operation reachable
+• eip712Domain(): no sensitive operation reachable [analysis incomplete for this function]
+• executeUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x4337084d9e255ff0702461cf8895ce9e3b5ff108; storage_condition
+• entryPoint(): no sensitive operation reachable
+• invalidateNonce(uint256): every path to a sensitive operation passes an authorization check — check found: self_call_check; storage_condition
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• supportsExecutionMode(bytes32): no sensitive operation reachable
+• execute(bytes32,bytes): an unauthenticated path to a sensitive operation exists — check found: signature_authorization; self_call_check [analysis incomplete for this function]
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG30" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=6792 bytes
+verified source=True
+other chains with identical bytecode: ["polygon"]
+on-chain storage read during evidence collection: [{"slot": "1581abf533ae210f1ff5d25f322511179a9a65d8d8e43c998eab264f924af900", "offset": 0, "type": "mapping(uint256 =&gt; uint64)", "n_reads": 3, "n_writes": 2}, {"slot": "1581abf533ae210f1ff5d25f322511179a9a65d8d8e43c998eab264f924af901", "offset": 0, "type": "mapping(address =&gt; bool)", "n_reads": 4, "
+addresses embedded in the code: [{"bytecode_offset": 696, "address": "0x4337084d9e255ff0702461cf8895ce9e3b5ff108"}]</t>
+        </is>
+      </c>
+      <c r="AH30" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CREATE2': [6763, 6769]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: eip712Domain(), execute(bytes32,bytes), validateUserOp((address,uint256,bytes,bytes,bytes32,uint256,bytes32,bytes,bytes),bytes32,uint256)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
@@ -4599,6 +6259,57 @@
       <c r="W31" s="9" t="inlineStr"/>
       <c r="X31" s="8" t="inlineStr"/>
       <c r="Y31" s="8" t="inlineStr"/>
+      <c r="Z31" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA31" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB31" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x6fbd0908: CALL at pc=133 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC31" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD31" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE31" s="12" t="inlineStr">
+        <is>
+          <t>1797-byte runtime on ethereum exposing 1 dispatched function(s): 0x6fbd0908
+Concern(s) found: 0x6fbd0908: CALL at pc=133 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Instruction census (whole contract): ADDRESS×1, CALL×2, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF31" s="12" t="inlineStr">
+        <is>
+          <t>• 0x6fbd0908: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG31" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1797 bytes
+verified source=True
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH31" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x6fbd0908 pc=486 -&gt; unresolved (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4726,6 +6437,57 @@
       <c r="W32" s="6" t="inlineStr"/>
       <c r="X32" s="8" t="inlineStr"/>
       <c r="Y32" s="8" t="inlineStr"/>
+      <c r="Z32" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA32" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB32" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [316], 'CALLCODE': [2612]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC32" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD32" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE32" s="12" t="inlineStr">
+        <is>
+          <t>2646-byte runtime on base exposing 1 dispatched function(s): executeBatch((address,uint256,bytes)[]) Embedded strings mention: BatchDelegator.
+Instruction census (whole contract): CALL×1, CALLCODE×1, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF32" s="12" t="inlineStr">
+        <is>
+          <t>• executeBatch((address,uint256,bytes)[]): no sensitive operation reachable [analysis incomplete for this function]
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG32" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2646 bytes
+verified source=False
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH32" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [316], 'CALLCODE': [2612]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: executeBatch((address,uint256,bytes)[])</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
@@ -4853,6 +6615,84 @@
       <c r="W33" s="9" t="inlineStr"/>
       <c r="X33" s="8" t="inlineStr"/>
       <c r="Y33" s="8" t="inlineStr"/>
+      <c r="Z33" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA33" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB33" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x04011f25: CALL at pc=957 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC33" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD33" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE33" s="12" t="inlineStr">
+        <is>
+          <t>9227-byte runtime on ethereum exposing 24 dispatched function(s): 0x04011f25, add(address), uniswapV2Call(address,uint256,uint256,bytes), onFlashLoan(address,address,uint256,uint256,bytes), 0x35a3290b, 0x3c55cfdc, 0x3ff8890a, executeOperation(address,address,uint256,uint256,bytes), enter(address,address), 0x6053b202 Embedded strings mention: Ownable.
+Concern(s) found: 0x04011f25: CALL at pc=957 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x35a3290b: CALL at pc=957 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x3ff8890a: CALL at pc=957 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call; 0x6888b009: CALL at pc=1746 with an attacker-chosen target (target from calldata) reachable with no authorization branch on any path from the dispatcher — an unauthorized caller can make the authorizing EOA execute an arbitrary call
+Protection(s) found: self-call restriction (msg.sender == address(this)) on initialize() — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; msg.sender compared against a stored authority on 0x3c55cfdc, 0x6053b202, 0xa9e7207d, DPPFlashLoanCall(address,uint256,uint256,bytes), DSPFlashLoanCall(address,uint256,uint256,bytes), DVMFlashLoanCall(address,uint256,uint256,bytes)
+Instruction census (whole contract): ADDRESS×36, CALL×10, CALLER×23, ORIGIN×18, SSTORE×2, STATICCALL×14</t>
+        </is>
+      </c>
+      <c r="AF33" s="12" t="inlineStr">
+        <is>
+          <t>• 0x04011f25: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• add(address): no sensitive operation reachable — check found: storage_based_caller_check; storage_based_caller_check
+• uniswapV2Call(address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• onFlashLoan(address,address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• 0x35a3290b: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• 0x3c55cfdc: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0x3ff8890a: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• executeOperation(address,address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• enter(address,address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• 0x6053b202: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• 0x6888b009: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• DPPFlashLoanCall(address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• initialize(): every path to a sensitive operation passes an authorization check — check found: self_call_check
+• 0x87060fd1: an unauthenticated path to a sensitive operation exists [analysis incomplete for this function]
+• hook(address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• pancakeV3FlashCallback(uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• 0xa9e7207d: every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• enter(address): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• st(address,address,uint256): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• DSPFlashLoanCall(address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• enter(): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check
+• uniswapV3FlashCallback(uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• DVMFlashLoanCall(address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_based_caller_check [analysis incomplete for this function]
+• receiveFlashLoan(address[],uint256[],uint256[],bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG33" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=9227 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 3, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "address", "n_reads": 18, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 1889, "address": "0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2"}, {"bytecode_offset": 2050, "address": "0xba12222222228d8ba445958a75a0704d566bf2c8"}]</t>
+        </is>
+      </c>
+      <c r="AH33" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [4532]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x04011f25, 0x35a3290b, 0x3ff8890a, 0x6053b202, 0x6888b009, 0x87060fd1, DPPFlashLoanCall(address,uint256,uint256,bytes), DSPFlashLoanCall(address,uint256,uint256,bytes); unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0x87060fd1 pc=957 -&gt; 0xba12222222228d8ba445958a75a0704d566bf2c8 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4960,6 +6800,58 @@
       <c r="W34" s="6" t="inlineStr"/>
       <c r="X34" s="8" t="inlineStr"/>
       <c r="Y34" s="8" t="inlineStr"/>
+      <c r="Z34" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA34" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB34" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=27 to 0x4d59cd593f6982fdb2eb08bb4e761514b320c14c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC34" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD34" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE34" s="12" t="inlineStr">
+        <is>
+          <t>38-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=27 to 0x4d59cd593f6982fdb2eb08bb4e761514b320c14c with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×1</t>
+        </is>
+      </c>
+      <c r="AF34" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG34" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=38 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 5, "address": "0x4d59cd593f6982fdb2eb08bb4e761514b320c14c"}]</t>
+        </is>
+      </c>
+      <c r="AH34" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
@@ -5087,6 +6979,57 @@
       <c r="W35" s="9" t="inlineStr"/>
       <c r="X35" s="8" t="inlineStr"/>
       <c r="Y35" s="8" t="inlineStr"/>
+      <c r="Z35" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA35" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB35" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [324]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC35" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD35" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE35" s="12" t="inlineStr">
+        <is>
+          <t>2854-byte runtime on base exposing 1 dispatched function(s): 0x89dd3dd6 Embedded strings mention: Signed Message.
+Instruction census (whole contract): ADDRESS×2, CALL×1, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF35" s="12" t="inlineStr">
+        <is>
+          <t>• 0x89dd3dd6: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG35" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=2854 bytes
+verified source=True
+other chains with identical bytecode: ["base"]</t>
+        </is>
+      </c>
+      <c r="AH35" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [324]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -5214,6 +7157,58 @@
       <c r="W36" s="6" t="inlineStr"/>
       <c r="X36" s="8" t="inlineStr"/>
       <c r="Y36" s="8" t="inlineStr"/>
+      <c r="Z36" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA36" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB36" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: send(): CALL at pc=109 to 0x734a5eec06146f4ed90a206124c593574d6182e4 with value from literal 100000, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC36" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD36" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE36" s="12" t="inlineStr">
+        <is>
+          <t>286-byte runtime on ethereum exposing 1 dispatched function(s): send()
+Concern(s) found: send(): CALL at pc=109 to 0x734a5eec06146f4ed90a206124c593574d6182e4 with value from literal 100000, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 1, 'ADDRESS': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): ADDRESS×1, CALL×1</t>
+        </is>
+      </c>
+      <c r="AF36" s="12" t="inlineStr">
+        <is>
+          <t>• send(): an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG36" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=286 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 41, "address": "0x734a5eec06146f4ed90a206124c593574d6182e4"}]</t>
+        </is>
+      </c>
+      <c r="AH36" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
@@ -5341,6 +7336,56 @@
       <c r="W37" s="9" t="inlineStr"/>
       <c r="X37" s="8" t="inlineStr"/>
       <c r="Y37" s="8" t="inlineStr"/>
+      <c r="Z37" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA37" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB37" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: every dispatched function analysed to completion with no reachable sensitive operation. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC37" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD37" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE37" s="12" t="inlineStr">
+        <is>
+          <t>463-byte runtime on ethereum exposing 2 dispatched function(s): ping(), initialize()</t>
+        </is>
+      </c>
+      <c r="AF37" s="12" t="inlineStr">
+        <is>
+          <t>• ping(): no sensitive operation reachable
+• initialize(): no sensitive operation reachable</t>
+        </is>
+      </c>
+      <c r="AG37" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=463 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH37" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -5468,6 +7513,61 @@
       <c r="W38" s="6" t="inlineStr"/>
       <c r="X38" s="8" t="inlineStr"/>
       <c r="Y38" s="8" t="inlineStr"/>
+      <c r="Z38" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA38" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB38" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [858, 2488], 'DELEGATECALL': [2518]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC38" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD38" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE38" s="12" t="inlineStr">
+        <is>
+          <t>2530-byte runtime on ethereum exposing 3 dispatched function(s): execute((address,uint256,bytes)[]), execute((address,uint256,bytes)[],bytes), nonce() Embedded strings mention: Signed Message.
+Protection(s) found: self-call restriction (msg.sender == address(this)) on execute((address,uint256,bytes)[]) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; signature-derived authorization branch (ecrecover) on execute((address,uint256,bytes)[],bytes)
+Instruction census (whole contract): ADDRESS×1, CALL×2, CALLER×3, DELEGATECALL×1, SSTORE×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF38" s="12" t="inlineStr">
+        <is>
+          <t>• execute((address,uint256,bytes)[]): every path to a sensitive operation passes an authorization check — check found: self_call_check; storage_condition [analysis incomplete for this function]
+• execute((address,uint256,bytes)[],bytes): every path to a sensitive operation passes an authorization check — check found: signature_authorization; storage_condition [analysis incomplete for this function]
+• nonce(): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 3 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG38" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2530 bytes
+verified source=True
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 1, "n_writes": 2}]</t>
+        </is>
+      </c>
+      <c r="AH38" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [858, 2488], 'DELEGATECALL': [2518]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: execute((address,uint256,bytes)[]), execute((address,uint256,bytes)[],bytes)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -5595,6 +7695,63 @@
       <c r="W39" s="9" t="inlineStr"/>
       <c r="X39" s="8" t="inlineStr"/>
       <c r="Y39" s="8" t="inlineStr"/>
+      <c r="Z39" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA39" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB39" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0b51f8d5: msg.sender must equal the hardcoded address 0xe2dc4277451c95261d56637ae0692f5fa16647b3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC39" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD39" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE39" s="12" t="inlineStr">
+        <is>
+          <t>4034-byte runtime on ethereum exposing 5 dispatched function(s): 0x0b51f8d5, withdrawNative(address), withdrawToken(address,address), owner(), 0xdf025ec6 Embedded strings mention: Not owner.
+Concern(s) found: 0x0b51f8d5: msg.sender must equal the hardcoded address 0xe2dc4277451c95261d56637ae0692f5fa16647b3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdrawNative(address): msg.sender must equal the hardcoded address 0xe2dc4277451c95261d56637ae0692f5fa16647b3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xdf025ec6: msg.sender must equal the hardcoded address 0xe2dc4277451c95261d56637ae0692f5fa16647b3. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×1, CALL×4, CALLER×5, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF39" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0b51f8d5: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe2dc4277451c95261d56637ae0692f5fa16647b3
+• withdrawNative(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe2dc4277451c95261d56637ae0692f5fa16647b3
+• withdrawToken(address,address): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0xdf025ec6: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xe2dc4277451c95261d56637ae0692f5fa16647b3
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG39" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=4034 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 279, "address": "0xe2dc4277451c95261d56637ae0692f5fa16647b3"}]</t>
+        </is>
+      </c>
+      <c r="AH39" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1641]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -5722,6 +7879,65 @@
       <c r="W40" s="6" t="inlineStr"/>
       <c r="X40" s="8" t="inlineStr"/>
       <c r="Y40" s="8" t="inlineStr"/>
+      <c r="Z40" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA40" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB40" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [4619, 4804, 6894, 7330], 'CREATE': [16025], 'CALLCODE': [16027]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC40" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD40" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE40" s="12" t="inlineStr">
+        <is>
+          <t>16041-byte runtime on base exposing 6 dispatched function(s): 0x0239ea3b, pancakeV3SwapCallback(int256,int256,bytes), 0x96fc3511, 0x978c64d0, 0xf58b8f78, uniswapV3SwapCallback(int256,int256,bytes) Embedded strings mention: Signed Message.
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0xf58b8f78; msg.sender compared against a stored authority on pancakeV3SwapCallback(int256,int256,bytes), uniswapV3SwapCallback(int256,int256,bytes)
+Instruction census (whole contract): ADDRESS×9, CALL×11, CALLCODE×1, CALLER×7, CREATE×1, SSTORE×2, STATICCALL×14</t>
+        </is>
+      </c>
+      <c r="AF40" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0239ea3b: no sensitive operation reachable
+• pancakeV3SwapCallback(int256,int256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• 0x96fc3511: no sensitive operation reachable
+• 0x978c64d0: no sensitive operation reachable [analysis incomplete for this function]
+• 0xf58b8f78: every path to a sensitive operation passes an authorization check — check found: signature_authorization; storage_condition
+• uniswapV3SwapCallback(int256,int256,bytes): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check; storage_condition
+• COVERAGE GAP: the analysis never reached 12 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG40" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=16041 bytes
+verified source=False
+other chains with identical bytecode: ["base", "bnb", "ethereum"]
+on-chain storage read during evidence collection: [{"slot": "f63006830011fe3ab565a55b23ad69c71bacfdf6525fac1274cfae5d71121e00", "offset": 0, "type": "mapping(uint256 =&gt; uint256)", "n_reads": 1, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 7155, "address": "0xfffd8963efd1fc6a506488495d951d5263988d26"}, {"bytecode_offset": 16001, "address": "0xfa219ea2f9db8449156c4be32b042b1bcaf0529e"}]</t>
+        </is>
+      </c>
+      <c r="AH40" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [4619, 4804, 6894, 7330], 'CREATE': [16025], 'CALLCODE': [16027]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x978c64d0</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
@@ -5849,6 +8065,58 @@
       <c r="W41" s="9" t="inlineStr"/>
       <c r="X41" s="8" t="inlineStr"/>
       <c r="Y41" s="8" t="inlineStr"/>
+      <c r="Z41" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA41" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB41" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on 0x6e54588a — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC41" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD41" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE41" s="12" t="inlineStr">
+        <is>
+          <t>1018-byte runtime on ethereum exposing 1 dispatched function(s): 0x6e54588a
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0x6e54588a — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF41" s="12" t="inlineStr">
+        <is>
+          <t>• 0x6e54588a: every path to a sensitive operation passes an authorization check — check found: self_call_check</t>
+        </is>
+      </c>
+      <c r="AG41" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1018 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 147, "address": "0xfd3f6daabfa7caaf812a616cec4c181dc6bb471d"}, {"bytecode_offset": 355, "address": "0x105083929bf9bb22c26cb1777ec92661170d4285"}]</t>
+        </is>
+      </c>
+      <c r="AH41" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -5976,6 +8244,63 @@
       <c r="W42" s="6" t="inlineStr"/>
       <c r="X42" s="8" t="inlineStr"/>
       <c r="Y42" s="8" t="inlineStr"/>
+      <c r="Z42" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA42" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB42" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x0b51f8d5: msg.sender must equal the hardcoded address 0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC42" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD42" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE42" s="12" t="inlineStr">
+        <is>
+          <t>5197-byte runtime on arbitrum exposing 5 dispatched function(s): 0x0b51f8d5, withdrawNative(address), withdrawToken(address,address), owner(), 0xdf025ec6
+Concern(s) found: 0x0b51f8d5: msg.sender must equal the hardcoded address 0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdrawNative(address): msg.sender must equal the hardcoded address 0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; 0xdf025ec6: msg.sender must equal the hardcoded address 0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×3, CALL×3, CALLER×4, DELEGATECALL×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF42" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0b51f8d5: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d
+• withdrawNative(address): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d
+• withdrawToken(address,address): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• 0xdf025ec6: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG42" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=5197 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum", "bnb", "optimism"]
+addresses embedded in the code: [{"bytecode_offset": 277, "address": "0x76e3d82b0c49f1c921d8c1093cd91c20ba23740d"}]</t>
+        </is>
+      </c>
+      <c r="AH42" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [2422, 3049]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
@@ -6103,6 +8428,57 @@
       <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="8" t="inlineStr"/>
       <c r="Y43" s="8" t="inlineStr"/>
+      <c r="Z43" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA43" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB43" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [148], 'DELEGATECALL': [610]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC43" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD43" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE43" s="12" t="inlineStr">
+        <is>
+          <t>649-byte runtime on ethereum exposing 1 dispatched function(s): transferToken(address,address,uint256)
+Instruction census (whole contract): CALL×1, CALLER×1, DELEGATECALL×1</t>
+        </is>
+      </c>
+      <c r="AF43" s="12" t="inlineStr">
+        <is>
+          <t>• transferToken(address,address,uint256): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG43" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=649 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH43" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [148], 'DELEGATECALL': [610]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -6230,6 +8606,58 @@
       <c r="W44" s="6" t="inlineStr"/>
       <c r="X44" s="8" t="inlineStr"/>
       <c r="Y44" s="8" t="inlineStr"/>
+      <c r="Z44" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA44" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB44" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: msg.sender compared against a stored authority on sendTokens(address,uint256) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC44" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD44" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE44" s="12" t="inlineStr">
+        <is>
+          <t>898-byte runtime on base exposing 1 dispatched function(s): sendTokens(address,uint256)
+Protection(s) found: msg.sender compared against a stored authority on sendTokens(address,uint256)
+Instruction census (whole contract): CALL×1, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF44" s="12" t="inlineStr">
+        <is>
+          <t>• sendTokens(address,uint256): every path to a sensitive operation passes an authorization check — check found: storage_based_caller_check</t>
+        </is>
+      </c>
+      <c r="AG44" s="12" t="inlineStr">
+        <is>
+          <t>chain=base
+runtime size=898 bytes
+verified source=False
+other chains with identical bytecode: ["base"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH44" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
@@ -6357,6 +8785,58 @@
       <c r="W45" s="9" t="inlineStr"/>
       <c r="X45" s="8" t="inlineStr"/>
       <c r="Y45" s="8" t="inlineStr"/>
+      <c r="Z45" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA45" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB45" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on 0x0ef296c1 — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC45" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD45" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE45" s="12" t="inlineStr">
+        <is>
+          <t>1363-byte runtime on bnb exposing 1 dispatched function(s): 0x0ef296c1
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0x0ef296c1 — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF45" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0ef296c1: every path to a sensitive operation passes an authorization check — check found: self_call_check; self_call_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG45" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=1363 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 94, "address": "0x5875e2bec7a034b84d11b8296fe509a4e1c5ff3b"}]</t>
+        </is>
+      </c>
+      <c r="AH45" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x0ef296c1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -6464,6 +8944,59 @@
       <c r="W46" s="6" t="inlineStr"/>
       <c r="X46" s="8" t="inlineStr"/>
       <c r="Y46" s="8" t="inlineStr"/>
+      <c r="Z46" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA46" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB46" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=69 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC46" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD46" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE46" s="12" t="inlineStr">
+        <is>
+          <t>1627-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: CALL at pc=69 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): ADDRESS×2, CALL×3, CALLER×1, ORIGIN×3, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF46" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists — check found: tx_origin_check; hardcoded_address_check against 0x36cfb3c2b0b14f75e9c7e407402a679f8293f216
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG46" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1627 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 191, "address": "0x36cfb3c2b0b14f75e9c7e407402a679f8293f216"}, {"bytecode_offset": 303, "address": "0xcda6461f1a30c618373f5790a83e1569fb685cba"}, {"bytecode_offset": 622, "address": "0x236501327e701692a281934230af0b6be8df3353"}]</t>
+        </is>
+      </c>
+      <c r="AH46" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [852]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
@@ -6591,6 +9124,60 @@
       <c r="W47" s="9" t="inlineStr"/>
       <c r="X47" s="8" t="inlineStr"/>
       <c r="Y47" s="8" t="inlineStr"/>
+      <c r="Z47" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA47" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB47" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on setImplementation(address) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC47" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD47" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE47" s="12" t="inlineStr">
+        <is>
+          <t>686-byte runtime on ethereum exposing 3 dispatched function(s): implementation(), owner(), setImplementation(address)
+Protection(s) found: self-call restriction (msg.sender == address(this)) on setImplementation(address) — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent
+Instruction census (whole contract): ADDRESS×1, CALLER×1, DELEGATECALL×1, SSTORE×1</t>
+        </is>
+      </c>
+      <c r="AF47" s="12" t="inlineStr">
+        <is>
+          <t>• implementation(): no sensitive operation reachable
+• owner(): no sensitive operation reachable
+• setImplementation(address): every path to a sensitive operation passes an authorization check — check found: self_call_check</t>
+        </is>
+      </c>
+      <c r="AG47" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=686 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 1, "n_writes": 1}]</t>
+        </is>
+      </c>
+      <c r="AH47" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -6718,6 +9305,59 @@
       <c r="W48" s="6" t="inlineStr"/>
       <c r="X48" s="8" t="inlineStr"/>
       <c r="Y48" s="8" t="inlineStr"/>
+      <c r="Z48" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA48" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB48" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: self-call restriction (msg.sender == address(this)) on 0xaa869d34 — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC48" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD48" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE48" s="12" t="inlineStr">
+        <is>
+          <t>2199-byte runtime on ethereum exposing 2 dispatched function(s): unlockCallback(bytes), 0xaa869d34
+Protection(s) found: self-call restriction (msg.sender == address(this)) on 0xaa869d34 — the canonical EIP-7702 owner check, satisfied only by a transaction the account itself sent; callback entry point(s) restricted to a fixed protocol address: unlockCallback(bytes) — caller restricted to Uniswap v4 PoolManager (0x000000000004444c5dc75cb358380d2e3de08a90), a known protocol contract — the prescribed pattern for a callback entry point
+Instruction census (whole contract): ADDRESS×3, CALL×10, CALLER×3</t>
+        </is>
+      </c>
+      <c r="AF48" s="12" t="inlineStr">
+        <is>
+          <t>• unlockCallback(bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x000000000004444c5dc75cb358380d2e3de08a90
+• 0xaa869d34: every path to a sensitive operation passes an authorization check — check found: self_call_check [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG48" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=2199 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 188, "address": "0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2"}, {"bytecode_offset": 409, "address": "0xe3c9e5b3f9cbd7a2beb01747172a87fae07e2e4a"}, {"bytecode_offset": 1123, "address": "0x105083929bf9bb22c26cb1777ec92661170d4285"}]</t>
+        </is>
+      </c>
+      <c r="AH48" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xaa869d34</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -6845,6 +9485,60 @@
       <c r="W49" s="9" t="inlineStr"/>
       <c r="X49" s="8" t="inlineStr"/>
       <c r="Y49" s="8" t="inlineStr"/>
+      <c r="Z49" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA49" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB49" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: signature-derived authorization branch (ecrecover) on 0x1c011d78, 0x963fbb22 The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC49" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD49" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE49" s="12" t="inlineStr">
+        <is>
+          <t>3205-byte runtime on arbitrum exposing 3 dispatched function(s): 0x1c011d78, usedNonces(uint256), 0x963fbb22
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x1c011d78, 0x963fbb22
+Instruction census (whole contract): ADDRESS×3, CALL×4, CALLER×1, ORIGIN×1, SSTORE×1, STATICCALL×3</t>
+        </is>
+      </c>
+      <c r="AF49" s="12" t="inlineStr">
+        <is>
+          <t>• 0x1c011d78: every path to a sensitive operation passes an authorization check — check found: tx_origin_check; storage_condition [analysis incomplete for this function]
+• usedNonces(uint256): no sensitive operation reachable
+• 0x963fbb22: every path to a sensitive operation passes an authorization check — check found: tx_origin_check; storage_condition</t>
+        </is>
+      </c>
+      <c r="AG49" s="12" t="inlineStr">
+        <is>
+          <t>chain=arbitrum
+runtime size=3205 bytes
+verified source=False
+other chains with identical bytecode: ["arbitrum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(uint256 =&gt; bool)", "n_reads": 3, "n_writes": 2}]</t>
+        </is>
+      </c>
+      <c r="AH49" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x1c011d78</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -6952,6 +9646,57 @@
       <c r="W50" s="6" t="inlineStr"/>
       <c r="X50" s="8" t="inlineStr"/>
       <c r="Y50" s="8" t="inlineStr"/>
+      <c r="Z50" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA50" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB50" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: msg.sender must equal the hardcoded address 0xd2306a7187fe8b0c0dee59b50fdc438d2075d24c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as PARTIALLY_CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC50" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed PARTIALLY_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD50" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer. An external call is reachable from the fallback/receive path but only behind an authorization branch, which is consistent with the rule staying silent (though the rule would have fired on reachability alone, so agreement here is coincidental rather than principled).</t>
+        </is>
+      </c>
+      <c r="AE50" s="12" t="inlineStr">
+        <is>
+          <t>1182-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: msg.sender must equal the hardcoded address 0xd2306a7187fe8b0c0dee59b50fdc438d2075d24c. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×7, CALLER×1, DELEGATECALL×2, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF50" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0xd2306a7187fe8b0c0dee59b50fdc438d2075d24c; storage_condition [analysis incomplete for this function]</t>
+        </is>
+      </c>
+      <c r="AG50" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1182 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH50" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: &lt;no dispatcher recovered; analysed from pc=0&gt; (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); &lt;no dispatcher recovered; analysed from pc=0&gt; (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); &lt;no dispatcher recovered; analysed from pc=0&gt; (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); &lt;no dispatcher recovered; analysed from pc=0&gt; (storage_condition (e.g. initialized flag, paused flag, or an authority slot)); analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: &lt;no dispatcher recovered; analysed from pc=0&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -7079,6 +9824,59 @@
       <c r="W51" s="9" t="inlineStr"/>
       <c r="X51" s="8" t="inlineStr"/>
       <c r="Y51" s="8" t="inlineStr"/>
+      <c r="Z51" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA51" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB51" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: multicall(address[],bytes[]): msg.sender must equal the hardcoded address 0x6c26d5ae5ea55735efbbc0ca9a4caf3c6753811d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC51" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD51" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE51" s="12" t="inlineStr">
+        <is>
+          <t>958-byte runtime on optimism exposing 2 dispatched function(s): multicall(address[],bytes[]), 0xa2ce10b4
+Concern(s) found: multicall(address[],bytes[]): msg.sender must equal the hardcoded address 0x6c26d5ae5ea55735efbbc0ca9a4caf3c6753811d. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): CALL×2, CALLER×2</t>
+        </is>
+      </c>
+      <c r="AF51" s="12" t="inlineStr">
+        <is>
+          <t>• multicall(address[],bytes[]): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x6c26d5ae5ea55735efbbc0ca9a4caf3c6753811d
+• 0xa2ce10b4: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG51" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=958 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]</t>
+        </is>
+      </c>
+      <c r="AH51" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [945]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7206,6 +10004,59 @@
       <c r="W52" s="6" t="inlineStr"/>
       <c r="X52" s="8" t="inlineStr"/>
       <c r="Y52" s="8" t="inlineStr"/>
+      <c r="Z52" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA52" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB52" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [832]}) — capability here is a lower bound The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC52" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD52" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE52" s="12" t="inlineStr">
+        <is>
+          <t>3536-byte runtime on polygon exposing 3 dispatched function(s): onERC721Received(address,address,uint256,bytes), onERC1155BatchReceived(address,address,uint256[],uint256[],bytes), onERC1155Received(address,address,uint256,uint256,bytes) Embedded strings mention: Router.
+Instruction census (whole contract): ADDRESS×1, CALL×1, CALLER×1, ORIGIN×2</t>
+        </is>
+      </c>
+      <c r="AF52" s="12" t="inlineStr">
+        <is>
+          <t>• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• onERC1155BatchReceived(address,address,uint256[],uint256[],bytes): no sensitive operation reachable
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 1 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG52" s="12" t="inlineStr">
+        <is>
+          <t>chain=polygon
+runtime size=3536 bytes
+verified source=False
+other chains with identical bytecode: ["polygon"]</t>
+        </is>
+      </c>
+      <c r="AH52" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [832]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -7333,6 +10184,83 @@
       <c r="W53" s="9" t="inlineStr"/>
       <c r="X53" s="8" t="inlineStr"/>
       <c r="Y53" s="8" t="inlineStr"/>
+      <c r="Z53" s="12" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="AA53" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB53" s="12" t="inlineStr">
+        <is>
+          <t>SAFE because positive authorization evidence was found and no unauthenticated path to a sensitive operation survived the guard-dominance test: signature-derived authorization branch (ecrecover) on 0x437d55db, 0x6bb0bfe2, 0x71e72d80, 0xd9828e82, cancelLimitOrder(bytes32,bytes) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC53" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD53" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE53" s="12" t="inlineStr">
+        <is>
+          <t>11341-byte runtime on optimism exposing 25 dispatched function(s): 0x0bb28465, isValidSignature(bytes32,bytes), 0x20320171, 0x20a4753b, 0x253c0c9d, 0x4149bc28, 0x437d55db, cancelLimitOrder(bytes32,bytes), 0x4fb655aa, 0x53f20a4f Embedded strings mention: Signed Message.
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0x437d55db, 0x6bb0bfe2, 0x71e72d80, 0xd9828e82, cancelLimitOrder(bytes32,bytes)
+Instruction census (whole contract): ADDRESS×18, CALL×11, CALLER×3, SSTORE×29, STATICCALL×8</t>
+        </is>
+      </c>
+      <c r="AF53" s="12" t="inlineStr">
+        <is>
+          <t>• 0x0bb28465: an unauthenticated path to a sensitive operation exists — check found: storage_condition
+• isValidSignature(bytes32,bytes): no sensitive operation reachable
+• 0x20320171: no sensitive operation reachable
+• 0x20a4753b: no sensitive operation reachable
+• 0x253c0c9d: no sensitive operation reachable — check found: storage_condition; storage_condition
+• 0x4149bc28: no sensitive operation reachable
+• 0x437d55db: every path to a sensitive operation passes an authorization check — check found: storage_condition; signature_authorization
+• cancelLimitOrder(bytes32,bytes): every path to a sensitive operation passes an authorization check — check found: storage_condition; storage_condition
+• 0x4fb655aa: no sensitive operation reachable
+• 0x53f20a4f: no sensitive operation reachable
+• 0x589f075c: no sensitive operation reachable
+• executedOrders(uint256): no sensitive operation reachable
+• 0x6bb0bfe2: every path to a sensitive operation passes an authorization check — check found: storage_condition; signature_authorization [analysis incomplete for this function]
+• 0x71e72d80: every path to a sensitive operation passes an authorization check — check found: signature_authorization
+• 0x78f197ad: no sensitive operation reachable
+• 0x7f545269: no sensitive operation reachable
+• 0x7f94dd33: no sensitive operation reachable
+• 0x8501bfb5: no sensitive operation reachable
+• 0x964566ec: no sensitive operation reachable
+• 0x9cf54c00: no sensitive operation reachable
+• 0xaae94f99: an unauthenticated path to a sensitive operation exists — check found: storage_condition; storage_condition
+• 0xaf87aaec: an unauthenticated path to a sensitive operation exists
+• nonce(): no sensitive operation reachable
+• 0xd29ca57c: no sensitive operation reachable
+• 0xd9828e82: every path to a sensitive operation passes an authorization check — check found: signature_authorization</t>
+        </is>
+      </c>
+      <c r="AG53" s="12" t="inlineStr">
+        <is>
+          <t>chain=optimism
+runtime size=11341 bytes
+verified source=False
+other chains with identical bytecode: ["optimism"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "uint256", "n_reads": 2, "n_writes": 1}, {"slot": "0000000000000000000000000000000000000000000000000000000000000001", "offset": 0, "type": "mapping(uint256 =&gt; bool)", "n_reads": 2, "n_writes": 1}, {"sl
+addresses embedded in the code: [{"bytecode_offset": 10119, "address": "0x13dc99195c881b9bdd081c9959da5cdd195c9959"}]</t>
+        </is>
+      </c>
+      <c r="AH53" s="12" t="inlineStr">
+        <is>
+          <t>analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0x6bb0bfe2; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0xaae94f99 pc=2836 -&gt; 0x2339f78e2ec15c47cf042f2460c532c0d7ff1cce (value=0, data=memory); 0xaae94f99 pc=2905 -&gt; unresolved (value=0, data=memory); 0xaf87aaec pc=1641 -&gt; unresolved (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -7440,6 +10368,58 @@
       <c r="W54" s="6" t="inlineStr"/>
       <c r="X54" s="8" t="inlineStr"/>
       <c r="Y54" s="8" t="inlineStr"/>
+      <c r="Z54" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA54" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB54" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: &lt;no dispatcher recovered; analysed from pc=0&gt;: DELEGATECALL at pc=94 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage The source static analyzer's verdict was assessed as CONTRADICTED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC54" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONTRADICTED</t>
+        </is>
+      </c>
+      <c r="AD54" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: The source analyzer did not flag this contract, yet an external call is reachable from the receive()/fallback() path without passing any caller authorization branch. `unflagged` is a weak signal by construction — the negatives in this dataset are rule-silent, never benignity-verified — so this is a plausible source-rule miss rather than a contradiction of a positive finding.</t>
+        </is>
+      </c>
+      <c r="AE54" s="12" t="inlineStr">
+        <is>
+          <t>171-byte runtime on ethereum exposing 0 dispatched function(s): &lt;no dispatcher recovered; analysed from pc=0&gt;
+Concern(s) found: &lt;no dispatcher recovered; analysed from pc=0&gt;: DELEGATECALL at pc=94 to ['sload'] reachable with no authorization branch — third-party code would execute against the EOA's own storage; the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'DELEGATECALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — DELEGATECALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): DELEGATECALL×1</t>
+        </is>
+      </c>
+      <c r="AF54" s="12" t="inlineStr">
+        <is>
+          <t>• &lt;no dispatcher recovered; analysed from pc=0&gt;: an unauthenticated path to a sensitive operation exists — check found: storage_condition</t>
+        </is>
+      </c>
+      <c r="AG54" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=171 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "address", "n_reads": 0, "n_writes": 0}]</t>
+        </is>
+      </c>
+      <c r="AH54" s="12" t="inlineStr">
+        <is>
+          <t>none identified</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
@@ -7567,6 +10547,64 @@
       <c r="W55" s="9" t="inlineStr"/>
       <c r="X55" s="8" t="inlineStr"/>
       <c r="Y55" s="8" t="inlineStr"/>
+      <c r="Z55" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN</t>
+        </is>
+      </c>
+      <c r="AA55" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="AB55" s="12" t="inlineStr">
+        <is>
+          <t>UNCERTAIN because the evidence does not establish either direction: the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined) The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC55" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD55" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE55" s="12" t="inlineStr">
+        <is>
+          <t>13884-byte runtime on bnb exposing 5 dispatched function(s): DOMAIN_SEPARATOR(), 0x54d5815f, 0x96fc3511, 0xf58b8f78, uniswapV3SwapCallback(int256,int256,bytes)
+Protection(s) found: signature-derived authorization branch (ecrecover) on 0xf58b8f78
+Instruction census (whole contract): ADDRESS×10, CALL×10, CALLER×3, CREATE×1, DELEGATECALL×1, SSTORE×1, STATICCALL×9</t>
+        </is>
+      </c>
+      <c r="AF55" s="12" t="inlineStr">
+        <is>
+          <t>• DOMAIN_SEPARATOR(): no sensitive operation reachable
+• 0x54d5815f: no sensitive operation reachable
+• 0x96fc3511: no sensitive operation reachable
+• 0xf58b8f78: no sensitive operation reachable — check found: signature_authorization
+• uniswapV3SwapCallback(int256,int256,bytes): every path to a sensitive operation passes an authorization check — check found: caller_check; caller_check
+• COVERAGE GAP: the analysis never reached 11 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG55" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=13884 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+on-chain storage read during evidence collection: [{"slot": "0000000000000000000000000000000000000000000000000000000000000000", "offset": 0, "type": "mapping(uint256 =&gt; uint256)", "n_reads": 2, "n_writes": 1}]
+addresses embedded in the code: [{"bytecode_offset": 6875, "address": "0xfffd8963efd1fc6a506488495d951d5263988d26"}, {"bytecode_offset": 8943, "address": "0xa6572f90309b9abca48c44cdf9cfe7cd77876911"}]</t>
+        </is>
+      </c>
+      <c r="AH55" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); uniswapV3SwapCallback(int256,int256,bytes) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); sensitive opcodes present in the bytecode that no traversal reached ({'DELEGATECALL': [9033], 'CALL': [9179, 9768, 9974, 10477], 'CREATE': [13867]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -7694,6 +10732,57 @@
       <c r="W56" s="6" t="inlineStr"/>
       <c r="X56" s="8" t="inlineStr"/>
       <c r="Y56" s="8" t="inlineStr"/>
+      <c r="Z56" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA56" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB56" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xbcd4cdad: CALL at pc=445 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC56" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD56" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE56" s="12" t="inlineStr">
+        <is>
+          <t>905-byte runtime on ethereum exposing 1 dispatched function(s): 0xbcd4cdad
+Concern(s) found: 0xbcd4cdad: CALL at pc=445 to unresolved with value from selfbalance, reachable with no authorization branch — moves funds the authorizing account already holds to a destination the account owner did not authorize at call time
+Instruction census (whole contract): CALL×2, CALLER×1, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF56" s="12" t="inlineStr">
+        <is>
+          <t>• 0xbcd4cdad: an unauthenticated path to a sensitive operation exists</t>
+        </is>
+      </c>
+      <c r="AG56" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=905 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH56" s="12" t="inlineStr">
+        <is>
+          <t>unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: 0xbcd4cdad pc=423 -&gt; 0x0000bbddc7ce488642fb579f8b00f3a590007251 (value=memory, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
@@ -7821,6 +10910,67 @@
       <c r="W57" s="9" t="inlineStr"/>
       <c r="X57" s="8" t="inlineStr"/>
       <c r="Y57" s="8" t="inlineStr"/>
+      <c r="Z57" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA57" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB57" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0x132db5ea: msg.sender must equal the hardcoded address 0x922cc241ee295ec37c048d5e3e2247bc54883998. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC57" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD57" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE57" s="12" t="inlineStr">
+        <is>
+          <t>7043-byte runtime on ethereum exposing 9 dispatched function(s): 0x132db5ea, onERC721Received(address,address,uint256,bytes), 0x58fc8604, 0x6ad1e989, destroy(), DVMFlashLoanCall(address,uint256,uint256,bytes), withdrawETH(uint256), onERC1155Received(address,address,uint256,uint256,bytes), depositETH()
+Concern(s) found: 0x132db5ea: msg.sender must equal the hardcoded address 0x922cc241ee295ec37c048d5e3e2247bc54883998. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; destroy(): msg.sender must equal the hardcoded address 0x922cc241ee295ec37c048d5e3e2247bc54883998. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; DVMFlashLoanCall(address,uint256,uint256,bytes): tx.origin must equal the hardcoded address 0x922cc241ee295ec37c048d5e3e2247bc54883998. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; withdrawETH(uint256): msg.sender must equal the hardcoded address 0x922cc241ee295ec37c048d5e3e2247bc54883998. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party; depositETH(): msg.sender must equal the hardcoded address 0x922cc241ee295ec37c048d5e3e2247bc54883998. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×3, CALL×7, CALLER×7, CREATE2×1, ORIGIN×1, SELFDESTRUCT×1, STATICCALL×5</t>
+        </is>
+      </c>
+      <c r="AF57" s="12" t="inlineStr">
+        <is>
+          <t>• 0x132db5ea: every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x922cc241ee295ec37c048d5e3e2247bc54883998
+• onERC721Received(address,address,uint256,bytes): no sensitive operation reachable
+• 0x58fc8604: no sensitive operation reachable
+• 0x6ad1e989: no sensitive operation reachable
+• destroy(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x922cc241ee295ec37c048d5e3e2247bc54883998
+• DVMFlashLoanCall(address,uint256,uint256,bytes): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x922cc241ee295ec37c048d5e3e2247bc54883998
+• withdrawETH(uint256): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x922cc241ee295ec37c048d5e3e2247bc54883998; caller_check
+• onERC1155Received(address,address,uint256,uint256,bytes): no sensitive operation reachable
+• depositETH(): every path to a sensitive operation passes an authorization check — check found: hardcoded_address_check against 0x922cc241ee295ec37c048d5e3e2247bc54883998
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG57" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=7043 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]
+addresses embedded in the code: [{"bytecode_offset": 650, "address": "0xc02aaa39b223fe8d0a0e5c4f27ead9083c756cc2"}, {"bytecode_offset": 2141, "address": "0x59728544b08ab483533076417fbbb2fd0b17ce3a"}, {"bytecode_offset": 7022, "address": "0x2f7fcf02f7f4468f2164736f6c634300081a0033"}]</t>
+        </is>
+      </c>
+      <c r="AH57" s="12" t="inlineStr">
+        <is>
+          <t>the only branch protecting a reachable sensitive operation compares msg.sender or tx.origin against a value the analyser could not resolve, so whether an attacker is excluded is undetermined: withdrawETH(uint256) (caller_check (msg.sender compared against an unresolved value); the analyser could not resolve what the caller is compared against, so whether this restricts an attacker is undetermined); sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1434], 'CREATE2': [7019]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -7948,6 +11098,61 @@
       <c r="W58" s="6" t="inlineStr"/>
       <c r="X58" s="8" t="inlineStr"/>
       <c r="Y58" s="8" t="inlineStr"/>
+      <c r="Z58" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA58" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="AB58" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: 0xb3021ef8: tx.origin must equal the hardcoded address 0xdeadbeef6f5dfc4675d3109b8a985e795de8083a. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC58" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD58" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE58" s="12" t="inlineStr">
+        <is>
+          <t>5460-byte runtime on bnb exposing 3 dispatched function(s): DPPFlashLoanCall(address,uint256,uint256,bytes), 0xb3021ef8, DVMFlashLoanCall(address,uint256,uint256,bytes) Embedded strings mention: not owner.
+Concern(s) found: 0xb3021ef8: tx.origin must equal the hardcoded address 0xdeadbeef6f5dfc4675d3109b8a985e795de8083a. That literal was fixed when the delegate was deployed, so it cannot be the authorizing EOA: this is not protection for the authorizer, it is exclusive privileged access for a fixed third party
+Instruction census (whole contract): ADDRESS×6, CALL×7, CALLER×2, ORIGIN×2, STATICCALL×4</t>
+        </is>
+      </c>
+      <c r="AF58" s="12" t="inlineStr">
+        <is>
+          <t>• DPPFlashLoanCall(address,uint256,uint256,bytes): an unauthenticated path to a sensitive operation exists
+• 0xb3021ef8: every path to a sensitive operation passes an authorization check — check found: tx.origin == msg.sender check; hardcoded_address_check against 0xdeadbeef6f5dfc4675d3109b8a985e795de8083a [analysis incomplete for this function]
+• DVMFlashLoanCall(address,uint256,uint256,bytes): an unauthenticated path to a sensitive operation exists
+• COVERAGE GAP: the analysis never reached 4 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG58" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=5460 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 383, "address": "0xdeadbeef6f5dfc4675d3109b8a985e795de8083a"}, {"bytecode_offset": 514, "address": "0x6098a5638d8d7e9ed2f952d35b2b67c34ec6b476"}, {"bytecode_offset": 559, "address": "0xbb4cdb9cbd36b01bd1cbaebf2de08d9173bc095c"}, {"bytecode_offset": 1757, "address": "0xb9e1fd5a02</t>
+        </is>
+      </c>
+      <c r="AH58" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1501, 1670, 2680, 3195]}) — capability here is a lower bound; analysis incomplete (unresolved dynamic jumps / exploration cap / stack underflow) for: 0xb3021ef8; unauthenticated call(s) to a fixed or stored destination whose payload is assembled in memory: DPPFlashLoanCall(address,uint256,uint256,bytes) pc=1919 -&gt; 0xbb4cdb9cbd36b01bd1cbaebf2de08d9173bc095c (value=0, data=memory); DPPFlashLoanCall(address,uint256,uint256,bytes) pc=2434 -&gt; 0x13f4ea83d0bd40e75c8222255bc855a974568dd4 (value=0, data=memory); DVMFlashLoanCall(address,uint256,uint256,bytes) pc=1919 -&gt; 0xbb4cdb9cbd36b01bd1cbaebf2de08d9173bc095c (value=0, data=memory); DVMFlashLoanCall(address,uint256,uint256,bytes) pc=2434 -&gt; 0x13f4ea83d0bd40e75c8222255bc855a974568dd4 (value=0, data=memory). This analyser does not track provenance through memory, so whether a caller can choose that payload — and therefore whether this is exploitable — is not established. Capability, not a demonstrated vulnerability.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
@@ -8075,6 +11280,60 @@
       <c r="W59" s="9" t="inlineStr"/>
       <c r="X59" s="8" t="inlineStr"/>
       <c r="Y59" s="8" t="inlineStr"/>
+      <c r="Z59" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA59" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB59" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 4, 'ADDRESS': 2, 'STATICCALL': 2, 'DELEGATECALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx4, DELEGATECALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC59" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD59" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE59" s="12" t="inlineStr">
+        <is>
+          <t>2082-byte runtime on bnb exposing 2 dispatched function(s): 0x8cabfe01, 0xe02bf96d
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 4, 'ADDRESS': 2, 'STATICCALL': 2, 'DELEGATECALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx4, DELEGATECALLx1 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): ADDRESS×2, CALL×4, DELEGATECALL×1, STATICCALL×2</t>
+        </is>
+      </c>
+      <c r="AF59" s="12" t="inlineStr">
+        <is>
+          <t>• 0x8cabfe01: no sensitive operation reachable
+• 0xe02bf96d: no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 5 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG59" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=2082 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]
+addresses embedded in the code: [{"bytecode_offset": 436, "address": "0xea459dde8dd4e1b28324ff1a1dcffedfec596db0"}]</t>
+        </is>
+      </c>
+      <c r="AH59" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [165, 499, 673, 1006], 'DELEGATECALL': [2039]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -8202,6 +11461,58 @@
       <c r="W60" s="6" t="inlineStr"/>
       <c r="X60" s="8" t="inlineStr"/>
       <c r="Y60" s="8" t="inlineStr"/>
+      <c r="Z60" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA60" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB60" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2, 'ADDRESS': 1, 'STATICCALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC60" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD60" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE60" s="12" t="inlineStr">
+        <is>
+          <t>1061-byte runtime on ethereum exposing 1 dispatched function(s): transfer(address,address)
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 2, 'ADDRESS': 1, 'STATICCALL': 1}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx2 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): ADDRESS×1, CALL×2, STATICCALL×1</t>
+        </is>
+      </c>
+      <c r="AF60" s="12" t="inlineStr">
+        <is>
+          <t>• transfer(address,address): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 2 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG60" s="12" t="inlineStr">
+        <is>
+          <t>chain=ethereum
+runtime size=1061 bytes
+verified source=False
+other chains with identical bytecode: ["ethereum"]</t>
+        </is>
+      </c>
+      <c r="AH60" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [184, 445]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
@@ -8329,6 +11640,66 @@
       <c r="W61" s="9" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
       <c r="Y61" s="8" t="inlineStr"/>
+      <c r="Z61" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE</t>
+        </is>
+      </c>
+      <c r="AA61" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AB61" s="12" t="inlineStr">
+        <is>
+          <t>UNSAFE because a concrete path exists from an externally reachable entry point to a sensitive operation that no authorization branch dominates: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 3}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx3 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored. The source static analyzer's verdict was assessed as CONFIRMED against this CFG evidence; it is treated as evidence, not as an automatic label, because the rule contains no authorization predicate.</t>
+        </is>
+      </c>
+      <c r="AC61" s="12" t="inlineStr">
+        <is>
+          <t>unflagged — assessed CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AD61" s="12" t="inlineStr">
+        <is>
+          <t>The original static analyzer did NOT flag this contract. That is a weak signal: it only means this one reachability pattern did not fire. The dataset's negatives are rule-silent delegates with no benignity verification of any kind, so 'unflagged' is not evidence of safety.
+Assessment against the control-flow evidence for this item: Not flagged by the source analyzer, and no external call is reachable from the receive()/fallback() path in the independent CFG re-derivation. Note this only means the one pattern the rule tests for is absent; it is not evidence of safety.</t>
+        </is>
+      </c>
+      <c r="AE61" s="12" t="inlineStr">
+        <is>
+          <t>4085-byte runtime on bnb exposing 9 dispatched function(s): name(), approve(address,uint256), totalSupply(), transferFrom(address,address,uint256), decimals(), balanceOf(address), symbol(), 0xd46adb8d, allowance(address,address) Embedded strings mention: Executor.
+Concern(s) found: the runtime contains no CALLER and no ORIGIN opcode anywhere (opcode census: {'CALL': 3}) and no path reaches ecrecover, so no msg.sender-, tx.origin- or signature-based access control can exist in it. Every capability it has — CALLx3 — is therefore reachable by an arbitrary caller. This conclusion follows from the opcode census alone and does not depend on how completely the control flow was explored.
+Instruction census (whole contract): CALL×3</t>
+        </is>
+      </c>
+      <c r="AF61" s="12" t="inlineStr">
+        <is>
+          <t>• name(): no sensitive operation reachable
+• approve(address,uint256): no sensitive operation reachable
+• totalSupply(): no sensitive operation reachable
+• transferFrom(address,address,uint256): no sensitive operation reachable
+• decimals(): no sensitive operation reachable
+• balanceOf(address): no sensitive operation reachable
+• symbol(): no sensitive operation reachable
+• 0xd46adb8d: no sensitive operation reachable
+• allowance(address,address): no sensitive operation reachable
+• COVERAGE GAP: the analysis never reached 3 sensitive instruction(s) that exist in this contract, so the list above is a lower bound on what it can do.</t>
+        </is>
+      </c>
+      <c r="AG61" s="12" t="inlineStr">
+        <is>
+          <t>chain=bnb
+runtime size=4085 bytes
+verified source=False
+other chains with identical bytecode: ["bnb"]</t>
+        </is>
+      </c>
+      <c r="AH61" s="12" t="inlineStr">
+        <is>
+          <t>sensitive opcodes present in the bytecode that no traversal reached ({'CALL': [1000, 1473, 4064]}) — capability here is a lower bound</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
